--- a/apps/mdm-platform/public/template.xlsx
+++ b/apps/mdm-platform/public/template.xlsx
@@ -68,7 +68,7 @@
     <t>MDM 字段台账导入模板</t>
   </si>
   <si>
-    <t>用于 /api/import/field-entries 批量导入字段台账</t>
+    <t>用于整理字段台账，具体办理入口与要求请以平台当前页面为准。</t>
   </si>
   <si>
     <t>必填列</t>
